--- a/Check_các_cuộc_thi/IOE/Lần 3/Thống kê IOE - Lần 3.xlsx
+++ b/Check_các_cuộc_thi/IOE/Lần 3/Thống kê IOE - Lần 3.xlsx
@@ -3697,7 +3697,7 @@
       </c>
       <c r="B126" s="7" t="inlineStr">
         <is>
-          <t>13/09/2013</t>
+          <t>Trần Hải Phong</t>
         </is>
       </c>
       <c r="C126" s="6" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="B127" s="7" t="inlineStr">
         <is>
-          <t>18/10/2014</t>
+          <t>Lê Ngọc Hân</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
@@ -3745,7 +3745,7 @@
       </c>
       <c r="B128" s="7" t="inlineStr">
         <is>
-          <t>2014-05-02 00:00:00</t>
+          <t>Đỗ Nguyễn Hà Minh</t>
         </is>
       </c>
       <c r="C128" s="6" t="inlineStr">
@@ -3769,7 +3769,7 @@
       </c>
       <c r="B129" s="7" t="inlineStr">
         <is>
-          <t>2014-04-09 00:00:00</t>
+          <t>Nguyễn Hoàng Hương Trà</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="B130" s="7" t="inlineStr">
         <is>
-          <t>26/6/2014</t>
+          <t>Bùi Mai Phương</t>
         </is>
       </c>
       <c r="C130" s="6" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="B131" s="7" t="inlineStr">
         <is>
-          <t>2014-09-09 00:00:00</t>
+          <t>Đỗ Trọng Hoàng</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
@@ -3841,7 +3841,7 @@
       </c>
       <c r="B132" s="7" t="inlineStr">
         <is>
-          <t>16/10/2014</t>
+          <t>Trần Đức Tài</t>
         </is>
       </c>
       <c r="C132" s="6" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="B134" s="7" t="inlineStr">
         <is>
-          <t>30/03/2013</t>
+          <t>Đỗ Tuệ Linh</t>
         </is>
       </c>
       <c r="C134" s="6" t="inlineStr">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="B135" s="7" t="inlineStr">
         <is>
-          <t>2013-02-02 00:00:00</t>
+          <t>Nguyễn Quang Hải Nam</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
@@ -3927,7 +3927,7 @@
       </c>
       <c r="B136" s="7" t="inlineStr">
         <is>
-          <t>2013-02-08 00:00:00</t>
+          <t>Phan Đức Việt</t>
         </is>
       </c>
       <c r="C136" s="6" t="inlineStr">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="B137" s="7" t="inlineStr">
         <is>
-          <t>2013-08-05 00:00:00</t>
+          <t>Nguyễn Quỳnh Chi</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="B138" s="7" t="inlineStr">
         <is>
-          <t>14/08/2013</t>
+          <t>Trần An Như</t>
         </is>
       </c>
       <c r="C138" s="6" t="inlineStr">
@@ -3999,7 +3999,7 @@
       </c>
       <c r="B139" s="7" t="inlineStr">
         <is>
-          <t>24/10/2013</t>
+          <t>Nguyễn Minh Thư</t>
         </is>
       </c>
       <c r="C139" s="6" t="inlineStr">
@@ -4023,7 +4023,7 @@
       </c>
       <c r="B140" s="7" t="inlineStr">
         <is>
-          <t>2013-05-09 00:00:00</t>
+          <t>Nguyễn Trần Khánh Dương</t>
         </is>
       </c>
       <c r="C140" s="6" t="inlineStr">
@@ -4047,7 +4047,7 @@
       </c>
       <c r="B141" s="7" t="inlineStr">
         <is>
-          <t>23/9/2013</t>
+          <t>Trần Lê Khánh An</t>
         </is>
       </c>
       <c r="C141" s="6" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="B142" s="7" t="inlineStr">
         <is>
-          <t>2013-04-06 00:00:00</t>
+          <t>Lê Bảo Minh</t>
         </is>
       </c>
       <c r="C142" s="6" t="inlineStr">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="B143" s="7" t="inlineStr">
         <is>
-          <t>28/02/2013</t>
+          <t>Nguyễn Nam Phong</t>
         </is>
       </c>
       <c r="C143" s="6" t="inlineStr">
@@ -7135,7 +7135,7 @@
       </c>
       <c r="B111" s="7" t="inlineStr">
         <is>
-          <t>13/09/2013</t>
+          <t>Trần Hải Phong</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
@@ -7156,7 +7156,7 @@
       </c>
       <c r="B112" s="7" t="inlineStr">
         <is>
-          <t>18/10/2014</t>
+          <t>Lê Ngọc Hân</t>
         </is>
       </c>
       <c r="C112" s="6" t="inlineStr">
@@ -7177,7 +7177,7 @@
       </c>
       <c r="B113" s="7" t="inlineStr">
         <is>
-          <t>2014-05-02 00:00:00</t>
+          <t>Đỗ Nguyễn Hà Minh</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="B114" s="7" t="inlineStr">
         <is>
-          <t>2014-04-09 00:00:00</t>
+          <t>Nguyễn Hoàng Hương Trà</t>
         </is>
       </c>
       <c r="C114" s="6" t="inlineStr">
@@ -7219,7 +7219,7 @@
       </c>
       <c r="B115" s="7" t="inlineStr">
         <is>
-          <t>26/6/2014</t>
+          <t>Bùi Mai Phương</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
@@ -7240,7 +7240,7 @@
       </c>
       <c r="B116" s="7" t="inlineStr">
         <is>
-          <t>2014-09-09 00:00:00</t>
+          <t>Đỗ Trọng Hoàng</t>
         </is>
       </c>
       <c r="C116" s="6" t="inlineStr">
@@ -7261,7 +7261,7 @@
       </c>
       <c r="B117" s="7" t="inlineStr">
         <is>
-          <t>16/10/2014</t>
+          <t>Trần Đức Tài</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="B121" s="7" t="inlineStr">
         <is>
-          <t>30/03/2013</t>
+          <t>Đỗ Tuệ Linh</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
@@ -7342,7 +7342,7 @@
       </c>
       <c r="B122" s="7" t="inlineStr">
         <is>
-          <t>2013-02-02 00:00:00</t>
+          <t>Nguyễn Quang Hải Nam</t>
         </is>
       </c>
       <c r="C122" s="6" t="inlineStr">
@@ -7363,7 +7363,7 @@
       </c>
       <c r="B123" s="7" t="inlineStr">
         <is>
-          <t>2013-02-08 00:00:00</t>
+          <t>Phan Đức Việt</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
@@ -7384,7 +7384,7 @@
       </c>
       <c r="B124" s="7" t="inlineStr">
         <is>
-          <t>2013-08-05 00:00:00</t>
+          <t>Nguyễn Quỳnh Chi</t>
         </is>
       </c>
       <c r="C124" s="6" t="inlineStr">
@@ -7405,7 +7405,7 @@
       </c>
       <c r="B125" s="7" t="inlineStr">
         <is>
-          <t>14/08/2013</t>
+          <t>Trần An Như</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="B126" s="7" t="inlineStr">
         <is>
-          <t>24/10/2013</t>
+          <t>Nguyễn Minh Thư</t>
         </is>
       </c>
       <c r="C126" s="6" t="inlineStr">
@@ -7447,7 +7447,7 @@
       </c>
       <c r="B127" s="7" t="inlineStr">
         <is>
-          <t>2013-05-09 00:00:00</t>
+          <t>Nguyễn Trần Khánh Dương</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
@@ -7468,7 +7468,7 @@
       </c>
       <c r="B128" s="7" t="inlineStr">
         <is>
-          <t>23/9/2013</t>
+          <t>Trần Lê Khánh An</t>
         </is>
       </c>
       <c r="C128" s="6" t="inlineStr">
@@ -7489,7 +7489,7 @@
       </c>
       <c r="B129" s="7" t="inlineStr">
         <is>
-          <t>2013-04-06 00:00:00</t>
+          <t>Lê Bảo Minh</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
@@ -7510,7 +7510,7 @@
       </c>
       <c r="B130" s="7" t="inlineStr">
         <is>
-          <t>28/02/2013</t>
+          <t>Nguyễn Nam Phong</t>
         </is>
       </c>
       <c r="C130" s="6" t="inlineStr">
